--- a/automate2/improved/reports/test_results.xlsx
+++ b/automate2/improved/reports/test_results.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,11 +52,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -87,9 +82,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -458,21 +450,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,11 +530,21 @@
           <t>เอกสารประกอบ</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Elapsed</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-266</t>
+          <t>TC-269</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -555,12 +559,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -570,12 +574,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Login ด้วย role Super Admin &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" &gt; กดปุ่มสร้าง/บันทึกรายการใหม่ &gt; กรอกข้อมูลและ Save</t>
+          <t>Login ด้วย role Admin &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" &gt; ตรวจสอบว่าเห็นข้อมูล/รายการ</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ระบบบันทึกข้อมูลสำเร็จ ไม่มี error เรื่องสิทธิ์</t>
+          <t>เห็นเมนูและสามารถดูข้อมูลได้ปกติ</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -585,308 +589,31 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>FAIL: Create/New button NOT FOUND in 'Point of Sale' (expected can create)</t>
+          <t>Error: Traceback (most recent call last):
+  File "C:\Users\gaykn\Downloads\automate2\improved\webapp\server.py", line 201, in _run_worker
+    status, comment = run_verification(
+                      ^^^^^^^</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-266_Super_Admin_Create.png</t>
+          <t>TC-269_Admin_Read.png</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC-270</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Accounting &amp; Finance</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>การขายสินค้าและบริการเงินสด (ขายสด)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Login ด้วย role Admin &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" (ถ้าเข้าได้จาก Read) &gt; พยายามหาปุ่มสร้าง/บันทึกรายการใหม่</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มีปุ่มสร้างรายการ หรือกดแล้วระบบแจ้งไม่มีสิทธิ์</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>PASS: 'Point of Sale' not accessible - Create button correctly unavailable</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-270_Admin_Create.png</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC-274</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Accounting &amp; Finance</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>การขายสินค้าและบริการเงินสด (ขายสด)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Login ด้วย role Supervisor &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" (ถ้าเข้าได้จาก Read) &gt; พยายามหาปุ่มสร้าง/บันทึกรายการใหม่</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มีปุ่มสร้างรายการ หรือกดแล้วระบบแจ้งไม่มีสิทธิ์</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>PASS: 'Point of Sale' not accessible - Create button correctly unavailable</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-274_Supervisor_Create.png</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC-278</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Accounting &amp; Finance</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>การขายสินค้าและบริการเงินสด (ขายสด)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Super User</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Login ด้วย role Super User &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" (ถ้าเข้าได้จาก Read) &gt; พยายามหาปุ่มสร้าง/บันทึกรายการใหม่</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มีปุ่มสร้างรายการ หรือกดแล้วระบบแจ้งไม่มีสิทธิ์</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>PASS: 'Point of Sale' not accessible - Create button correctly unavailable</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-278_Super_User_Create.png</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC-282</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Accounting &amp; Finance</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>การขายสินค้าและบริการเงินสด (ขายสด)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>User(Cashier)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Login ด้วย role User(Cashier) &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" (ถ้าเข้าได้จาก Read) &gt; พยายามหาปุ่มสร้าง/บันทึกรายการใหม่</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มีปุ่มสร้างรายการ หรือกดแล้วระบบแจ้งไม่มีสิทธิ์</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>PASS: 'Point of Sale' not accessible - Create button correctly unavailable</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-282_User(Cashier)_Create.png</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC-286</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Accounting &amp; Finance</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>การขายสินค้าและบริการเงินสด (ขายสด)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Outsource</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Login ด้วย role Outsource &gt; เข้าเมนู "การขายสินค้าและบริการเงินสด (ขายสด)" (ถ้าเข้าได้จาก Read) &gt; พยายามหาปุ่มสร้าง/บันทึกรายการใหม่</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มีปุ่มสร้างรายการ หรือกดแล้วระบบแจ้งไม่มีสิทธิ์</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>PASS: 'Point of Sale' not accessible - Create button correctly unavailable</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>c:\Users\gaykn\Downloads\automate2\improved\screenshots\TC-286_Outsource_Create.png</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>0.0s</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Point of Sale</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -897,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -907,7 +634,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>BOM UAT Automation Report</t>
         </is>
@@ -921,7 +648,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:36</t>
+          <t>2026-08-10 19:13</t>
         </is>
       </c>
     </row>
@@ -946,7 +673,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -961,11 +688,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -980,7 +707,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1025,14 +752,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -1071,90 +798,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Outsource</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Super Admin</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Super User</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>User(Cashier)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/automate2/improved/reports/test_results.xlsx
+++ b/automate2/improved/reports/test_results.xlsx
@@ -590,9 +590,9 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Error: Traceback (most recent call last):
-  File "C:\Users\gaykn\Downloads\automate2\improved\webapp\server.py", line 201, in _run_worker
-    status, comment = run_verification(
-                      ^^^^^^^</t>
+  File "C:\Users\gaykn\Downloads\autobom\AUTOMATEBOM\automate2\improved\webapp\server.py", line 238, in _run_worker
+    _state["total"] = total
+    _broadcast("</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 19:13</t>
+          <t>2026-08-10 21:29</t>
         </is>
       </c>
     </row>
